--- a/rooms-finish-painter-by-room-name-sample/rooms-finish-painter-by-room-name-sample.xlsx
+++ b/rooms-finish-painter-by-room-name-sample/rooms-finish-painter-by-room-name-sample.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\archdz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\core\projects\github\dynamobim-toolkit\rooms-finish-painter-by-room-name-sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838941AB-F30A-4C16-BCE9-AD5910549204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDB023D-CFF3-445A-8445-90219CEE7456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,9 +441,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -457,7 +463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -471,7 +477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -485,7 +491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -499,7 +505,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -513,7 +519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -527,7 +533,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -541,7 +547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -555,7 +561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -569,7 +575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -583,7 +589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
